--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:16:05+00:00</t>
+    <t>2026-09-16T05:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T05:34:40+00:00</t>
+    <t>2026-09-17T07:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:46:21+00:00</t>
+    <t>2026-09-17T12:50:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:50:52+00:00</t>
+    <t>2026-09-18T07:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:26:42+00:00</t>
+    <t>2026-09-29T15:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:00:21+00:00</t>
+    <t>2026-09-30T11:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T11:14:45+00:00</t>
+    <t>2026-09-30T12:38:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:38:12+00:00</t>
+    <t>2026-09-30T12:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T12:52:09+00:00</t>
+    <t>2026-09-30T14:46:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T14:46:14+00:00</t>
+    <t>2026-10-01T13:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:01:54+00:00</t>
+    <t>2026-10-02T12:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T12:58:24+00:00</t>
+    <t>2026-10-07T14:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T14:48:24+00:00</t>
+    <t>2026-10-08T12:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T12:55:57+00:00</t>
+    <t>2026-10-08T13:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T13:59:28+00:00</t>
+    <t>2026-10-08T14:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:12:43+00:00</t>
+    <t>2026-10-08T15:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
